--- a/slide_classification/TCGA_Results/TITAN/Conch1_5/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/TITAN/Conch1_5/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
@@ -1598,7 +1598,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2498,10 +2498,10 @@
         <v>0.838805</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J48" t="n">
         <v>1</v>
@@ -4132,10 +4132,10 @@
         <v>0.853587</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J86" t="n">
         <v>1</v>
@@ -4780,7 +4780,7 @@
         <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>0.666667</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
         <v>1</v>
@@ -6841,10 +6841,10 @@
         <v>0.327184</v>
       </c>
       <c r="H149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I149" t="n">
-        <v>0.333333</v>
+        <v>0.666667</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -7231,7 +7231,7 @@
         <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -8604,10 +8604,10 @@
         <v>0.880802</v>
       </c>
       <c r="H190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J190" t="n">
         <v>1</v>
@@ -14154,7 +14154,7 @@
         <v>0</v>
       </c>
       <c r="I319" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J319" t="n">
         <v>0</v>
@@ -17422,7 +17422,7 @@
         <v>0</v>
       </c>
       <c r="I395" t="n">
-        <v>0</v>
+        <v>0.333333</v>
       </c>
       <c r="J395" t="n">
         <v>1</v>
@@ -17763,10 +17763,10 @@
         <v>0.883512</v>
       </c>
       <c r="H403" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I403" t="n">
-        <v>0.666667</v>
+        <v>0.333333</v>
       </c>
       <c r="J403" t="n">
         <v>1</v>

--- a/slide_classification/TCGA_Results/TITAN/Conch1_5/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/TITAN/Conch1_5/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -517,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.494783</v>
+        <v>0.493416</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.97668</v>
+        <v>0.998293</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.219466</v>
+        <v>0.152323</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -646,7 +646,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.83944</v>
+        <v>0.7924330000000001</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.493209</v>
+        <v>0.432747</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.754933</v>
+        <v>0.686419</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.376387</v>
+        <v>0.24213</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -818,7 +818,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.619086</v>
+        <v>0.62705</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.698408</v>
+        <v>0.560352</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.294577</v>
+        <v>0.1436</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.996285</v>
+        <v>0.999767</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.321292</v>
+        <v>0.205078</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.57058</v>
+        <v>0.569859</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.284427</v>
+        <v>0.396944</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1119,7 +1119,7 @@
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7724299999999999</v>
+        <v>0.7498629999999999</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.441257</v>
+        <v>0.371312</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.326353</v>
+        <v>0.188314</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.160777</v>
+        <v>0.194509</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.145388</v>
+        <v>0.20021</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.179612</v>
+        <v>0.220604</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.870383</v>
+        <v>0.892506</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.341307</v>
+        <v>0.27685</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.335949</v>
+        <v>0.299434</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1503,10 +1503,10 @@
         <v>0.002937</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.579508</v>
+        <v>0.475305</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.291995</v>
+        <v>0.220852</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.274872</v>
+        <v>0.345276</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.457566</v>
+        <v>0.469537</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.737666</v>
+        <v>0.698727</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.997144</v>
+        <v>0.999631</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.462454</v>
+        <v>0.270412</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1804,10 +1804,10 @@
         <v>0.637823</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.596004</v>
+        <v>0.358818</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.447319</v>
+        <v>0.475096</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1890,10 +1890,10 @@
         <v>0.000326</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0.473844</v>
+        <v>0.731533</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2465</v>
+        <v>0.400204</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.475374</v>
+        <v>0.354639</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.304971</v>
+        <v>0.160281</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2062,10 +2062,10 @@
         <v>0.017501</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.621496</v>
+        <v>0.428611</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.192603</v>
+        <v>0.171543</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.369447</v>
+        <v>0.23292</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.307441</v>
+        <v>0.186919</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.216671</v>
+        <v>0.231465</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.115193</v>
+        <v>0.228496</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.373467</v>
+        <v>0.332642</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2366,7 +2366,7 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0.281014</v>
+        <v>0.406564</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.222853</v>
+        <v>0.468587</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.443707</v>
+        <v>0.421878</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0.838805</v>
+        <v>0.872161</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.310124</v>
+        <v>0.412278</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0.792342</v>
+        <v>0.876287</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2621,10 +2621,10 @@
         <v>0.07241300000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.520084</v>
+        <v>0.454304</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -2667,7 +2667,7 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0.991502</v>
+        <v>0.999969</v>
       </c>
       <c r="H52" t="n">
         <v>1</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.381241</v>
+        <v>0.210056</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2750,10 +2750,10 @@
         <v>0.028478</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.5270010000000001</v>
+        <v>0.361398</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.387766</v>
+        <v>0.386212</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.183828</v>
+        <v>0.14941</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2879,10 +2879,10 @@
         <v>1.4e-05</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.515549</v>
+        <v>0.410099</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.379588</v>
+        <v>0.365191</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0.451048</v>
+        <v>0.359334</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0.37121</v>
+        <v>0.341724</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0.998627</v>
+        <v>0.999992</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.444277</v>
+        <v>0.482772</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -3140,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.985278</v>
+        <v>0.998726</v>
       </c>
       <c r="H63" t="n">
         <v>1</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.409992</v>
+        <v>0.278347</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -3226,7 +3226,7 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0.7083700000000001</v>
+        <v>0.585622</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.326611</v>
+        <v>0.232587</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.362735</v>
+        <v>0.32795</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -3352,10 +3352,10 @@
         <v>0.415668</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0.466069</v>
+        <v>0.56071</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0.47587</v>
+        <v>0.494434</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.31645</v>
+        <v>0.184683</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -3484,7 +3484,7 @@
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0.563092</v>
+        <v>0.646614</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.38286</v>
+        <v>0.390258</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.284123</v>
+        <v>0.27035</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.493915</v>
+        <v>0.446455</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3656,7 +3656,7 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0.393383</v>
+        <v>0.403062</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>0.723787</v>
+        <v>0.668386</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3742,7 +3742,7 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.9298650000000001</v>
+        <v>0.915364</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3785,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.40702</v>
+        <v>0.421103</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3828,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.347851</v>
+        <v>0.225265</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3871,7 +3871,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.449213</v>
+        <v>0.418489</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.204991</v>
+        <v>0.184401</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3954,10 +3954,10 @@
         <v>0.002696</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>0.579393</v>
+        <v>0.402568</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -4000,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.322337</v>
+        <v>0.153085</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.451673</v>
+        <v>0.28888</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.318955</v>
+        <v>0.308259</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -4129,7 +4129,7 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>0.853587</v>
+        <v>0.956851</v>
       </c>
       <c r="H86" t="n">
         <v>1</v>
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.247195</v>
+        <v>0.189927</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -4215,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0.267472</v>
+        <v>0.215512</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -4258,7 +4258,7 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0.8611529999999999</v>
+        <v>0.79001</v>
       </c>
       <c r="H89" t="n">
         <v>1</v>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.28643</v>
+        <v>0.125671</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0.401259</v>
+        <v>0.237376</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0.346633</v>
+        <v>0.296646</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -4430,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.444503</v>
+        <v>0.364386</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0.330593</v>
+        <v>0.412854</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0.416889</v>
+        <v>0.232025</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0.419861</v>
+        <v>0.373449</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.218082</v>
+        <v>0.183758</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -4645,7 +4645,7 @@
         <v>0</v>
       </c>
       <c r="G98" t="n">
-        <v>0.353479</v>
+        <v>0.219914</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -4688,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0.860316</v>
+        <v>0.9232590000000001</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0.393527</v>
+        <v>0.310784</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0.8601220000000001</v>
+        <v>0.924709</v>
       </c>
       <c r="H101" t="n">
         <v>1</v>
@@ -4817,7 +4817,7 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0.657878</v>
+        <v>0.788942</v>
       </c>
       <c r="H102" t="n">
         <v>1</v>
@@ -4860,7 +4860,7 @@
         <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>0.282566</v>
+        <v>0.222234</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0.280206</v>
+        <v>0.222237</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0.241752</v>
+        <v>0.259633</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.253702</v>
+        <v>0.347627</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.360567</v>
+        <v>0.497565</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.995243</v>
+        <v>0.8445240000000001</v>
       </c>
       <c r="H108" t="n">
         <v>1</v>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0.17495</v>
+        <v>0.182492</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0.779303</v>
+        <v>0.694307</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.151273</v>
+        <v>0.147335</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.299618</v>
+        <v>0.248111</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.174631</v>
+        <v>0.314573</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.349806</v>
+        <v>0.365464</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>0.535718</v>
+        <v>0.530273</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.312206</v>
+        <v>0.361344</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>0.307808</v>
+        <v>0.48257</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.231051</v>
+        <v>0.249041</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -5545,10 +5545,10 @@
         <v>0.36853</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0.233152</v>
+        <v>0.609073</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.39837</v>
+        <v>0.267156</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>0.7518899999999999</v>
+        <v>0.6246</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5677,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.949839</v>
+        <v>0.84721</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -5720,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.799179</v>
+        <v>0.588099</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.168003</v>
+        <v>0.133162</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.230606</v>
+        <v>0.210612</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.447079</v>
+        <v>0.270352</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.181828</v>
+        <v>0.181909</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.262497</v>
+        <v>0.222791</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -5975,10 +5975,10 @@
         <v>0.021908</v>
       </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G129" t="n">
-        <v>0.685101</v>
+        <v>0.38761</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -6018,10 +6018,10 @@
         <v>0.93403</v>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>0.4317</v>
+        <v>0.53208</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0.221666</v>
+        <v>0.246059</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.223336</v>
+        <v>0.186959</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.179535</v>
+        <v>0.185634</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.315994</v>
+        <v>0.254769</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.245628</v>
+        <v>0.146465</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.147475</v>
+        <v>0.178642</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.240404</v>
+        <v>0.26036</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.293122</v>
+        <v>0.229701</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.227744</v>
+        <v>0.28146</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.194102</v>
+        <v>0.174187</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -6494,7 +6494,7 @@
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>0.516014</v>
+        <v>0.6555530000000001</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -6534,10 +6534,10 @@
         <v>7.1e-05</v>
       </c>
       <c r="F142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.508832</v>
+        <v>0.392739</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -6580,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.208758</v>
+        <v>0.195679</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6623,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.23203</v>
+        <v>0.183871</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.157729</v>
+        <v>0.225878</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -6709,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.389225</v>
+        <v>0.336491</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -6752,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.152232</v>
+        <v>0.273095</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.230043</v>
+        <v>0.159817</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6838,7 +6838,7 @@
         <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.327184</v>
+        <v>0.425692</v>
       </c>
       <c r="H149" t="n">
         <v>1</v>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.312011</v>
+        <v>0.259915</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6924,7 +6924,7 @@
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>0.707027</v>
+        <v>0.654104</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.999851</v>
+        <v>0.986722</v>
       </c>
       <c r="H152" t="n">
         <v>1</v>
@@ -7010,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.113815</v>
+        <v>0.192951</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -7053,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0.190913</v>
+        <v>0.281763</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.366443</v>
+        <v>0.33972</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.27074</v>
+        <v>0.248215</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>0.42796</v>
+        <v>0.282796</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -7225,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0.318719</v>
+        <v>0.295259</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.240515</v>
+        <v>0.194227</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>0.199503</v>
+        <v>0.238594</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.245049</v>
+        <v>0.228679</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7397,7 +7397,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0.224794</v>
+        <v>0.168626</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>0.230507</v>
+        <v>0.336617</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>0.995304</v>
+        <v>0.9568680000000001</v>
       </c>
       <c r="H164" t="n">
         <v>1</v>
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.260739</v>
+        <v>0.306691</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>0.959273</v>
+        <v>0.843001</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0.201092</v>
+        <v>0.248364</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -7655,7 +7655,7 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0.999004</v>
+        <v>0.652103</v>
       </c>
       <c r="H168" t="n">
         <v>1</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0.152945</v>
+        <v>0.177647</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.185868</v>
+        <v>0.217518</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>0.365061</v>
+        <v>0.427635</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0.140497</v>
+        <v>0.150709</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -7870,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.249684</v>
+        <v>0.380828</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.172987</v>
+        <v>0.127322</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -7956,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.160837</v>
+        <v>0.172626</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>0.18648</v>
+        <v>0.21269</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.279456</v>
+        <v>0.319085</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0.132268</v>
+        <v>0.166197</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>0.140684</v>
+        <v>0.156708</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>0.098078</v>
+        <v>0.105492</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>0.403715</v>
+        <v>0.357299</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>0.463305</v>
+        <v>0.272087</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -8300,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>0.06374299999999999</v>
+        <v>0.121202</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0.123676</v>
+        <v>0.150817</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.2208</v>
+        <v>0.232508</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>0.142217</v>
+        <v>0.139851</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -8472,7 +8472,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>0.198617</v>
+        <v>0.09656000000000001</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>0.288011</v>
+        <v>0.249072</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>0.155662</v>
+        <v>0.266352</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -8601,7 +8601,7 @@
         <v>1</v>
       </c>
       <c r="G190" t="n">
-        <v>0.880802</v>
+        <v>0.7419</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -8644,7 +8644,7 @@
         <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>0.382412</v>
+        <v>0.494549</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -8687,7 +8687,7 @@
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>0.364185</v>
+        <v>0.37936</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -8730,7 +8730,7 @@
         <v>1</v>
       </c>
       <c r="G193" t="n">
-        <v>0.527909</v>
+        <v>0.746235</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -8773,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0.207459</v>
+        <v>0.14846</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>0.138423</v>
+        <v>0.110734</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -8859,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>0.261103</v>
+        <v>0.290075</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -8902,7 +8902,7 @@
         <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0.995605</v>
+        <v>0.901803</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0.542605</v>
+        <v>0.5632470000000001</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -8988,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="G199" t="n">
-        <v>0.948307</v>
+        <v>0.956319</v>
       </c>
       <c r="H199" t="n">
         <v>1</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>0.106674</v>
+        <v>0.185829</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>0.277378</v>
+        <v>0.229519</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -13933,7 +13933,7 @@
         <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>0.239386</v>
+        <v>0.184632</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -13976,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="G315" t="n">
-        <v>0.182926</v>
+        <v>0.274521</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -14019,7 +14019,7 @@
         <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>0.133898</v>
+        <v>0.200275</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -14062,7 +14062,7 @@
         <v>0</v>
       </c>
       <c r="G317" t="n">
-        <v>0.30708</v>
+        <v>0.292636</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -14105,7 +14105,7 @@
         <v>0</v>
       </c>
       <c r="G318" t="n">
-        <v>0.108556</v>
+        <v>0.32285</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -14148,7 +14148,7 @@
         <v>1</v>
       </c>
       <c r="G319" t="n">
-        <v>0.647979</v>
+        <v>0.608188</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -14191,7 +14191,7 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>0.853573</v>
+        <v>0.679034</v>
       </c>
       <c r="H320" t="n">
         <v>1</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="G321" t="n">
-        <v>0.354541</v>
+        <v>0.341319</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -14277,7 +14277,7 @@
         <v>0</v>
       </c>
       <c r="G322" t="n">
-        <v>0.268349</v>
+        <v>0.365529</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -14320,7 +14320,7 @@
         <v>0</v>
       </c>
       <c r="G323" t="n">
-        <v>0.206795</v>
+        <v>0.173336</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -14363,7 +14363,7 @@
         <v>0</v>
       </c>
       <c r="G324" t="n">
-        <v>0.245245</v>
+        <v>0.170752</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -14406,7 +14406,7 @@
         <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>0.223084</v>
+        <v>0.312982</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -14449,7 +14449,7 @@
         <v>0</v>
       </c>
       <c r="G326" t="n">
-        <v>0.385874</v>
+        <v>0.373598</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -14489,10 +14489,10 @@
         <v>0.016371</v>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G327" t="n">
-        <v>0.538888</v>
+        <v>0.395205</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -14535,7 +14535,7 @@
         <v>1</v>
       </c>
       <c r="G328" t="n">
-        <v>0.984556</v>
+        <v>0.863209</v>
       </c>
       <c r="H328" t="n">
         <v>0</v>
@@ -14578,7 +14578,7 @@
         <v>0</v>
       </c>
       <c r="G329" t="n">
-        <v>0.203069</v>
+        <v>0.203878</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -14621,7 +14621,7 @@
         <v>0</v>
       </c>
       <c r="G330" t="n">
-        <v>0.196471</v>
+        <v>0.188208</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -14664,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="G331" t="n">
-        <v>0.990507</v>
+        <v>0.975716</v>
       </c>
       <c r="H331" t="n">
         <v>0</v>
@@ -14707,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>0.2527</v>
+        <v>0.271161</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -14750,7 +14750,7 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0.999806</v>
+        <v>0.998734</v>
       </c>
       <c r="H333" t="n">
         <v>1</v>
@@ -14793,7 +14793,7 @@
         <v>1</v>
       </c>
       <c r="G334" t="n">
-        <v>0.561393</v>
+        <v>0.638302</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -14836,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>0.400569</v>
+        <v>0.261733</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -14876,10 +14876,10 @@
         <v>0.000392</v>
       </c>
       <c r="F336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>0.322636</v>
+        <v>0.567443</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14922,7 +14922,7 @@
         <v>0</v>
       </c>
       <c r="G337" t="n">
-        <v>0.155848</v>
+        <v>0.349111</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -14965,7 +14965,7 @@
         <v>0</v>
       </c>
       <c r="G338" t="n">
-        <v>0.121123</v>
+        <v>0.190775</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="G339" t="n">
-        <v>0.140914</v>
+        <v>0.215288</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -15051,7 +15051,7 @@
         <v>0</v>
       </c>
       <c r="G340" t="n">
-        <v>0.165629</v>
+        <v>0.366452</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -15094,7 +15094,7 @@
         <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>0.152629</v>
+        <v>0.264869</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -15137,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>0.243412</v>
+        <v>0.237708</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -15180,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>0.163357</v>
+        <v>0.157516</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -15223,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="G344" t="n">
-        <v>0.101545</v>
+        <v>0.259363</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -15266,7 +15266,7 @@
         <v>1</v>
       </c>
       <c r="G345" t="n">
-        <v>0.779433</v>
+        <v>0.653635</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -15306,10 +15306,10 @@
         <v>0.020983</v>
       </c>
       <c r="F346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G346" t="n">
-        <v>0.416877</v>
+        <v>0.551594</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -15352,7 +15352,7 @@
         <v>0</v>
       </c>
       <c r="G347" t="n">
-        <v>0.336578</v>
+        <v>0.366102</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -15395,7 +15395,7 @@
         <v>1</v>
       </c>
       <c r="G348" t="n">
-        <v>0.647681</v>
+        <v>0.620355</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -15435,10 +15435,10 @@
         <v>0.007205</v>
       </c>
       <c r="F349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G349" t="n">
-        <v>0.724415</v>
+        <v>0.44679</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -15481,7 +15481,7 @@
         <v>1</v>
       </c>
       <c r="G350" t="n">
-        <v>0.520651</v>
+        <v>0.7758350000000001</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -15524,7 +15524,7 @@
         <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>0.376655</v>
+        <v>0.409406</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -15567,7 +15567,7 @@
         <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>0.213978</v>
+        <v>0.249989</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -15610,7 +15610,7 @@
         <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>0.191503</v>
+        <v>0.190797</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -15653,7 +15653,7 @@
         <v>0</v>
       </c>
       <c r="G354" t="n">
-        <v>0.282472</v>
+        <v>0.442728</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -15696,7 +15696,7 @@
         <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>0.237259</v>
+        <v>0.221648</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>0</v>
       </c>
       <c r="G356" t="n">
-        <v>0.235987</v>
+        <v>0.253176</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -15782,7 +15782,7 @@
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>0.30672</v>
+        <v>0.21747</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -15825,7 +15825,7 @@
         <v>1</v>
       </c>
       <c r="G358" t="n">
-        <v>0.989955</v>
+        <v>0.929608</v>
       </c>
       <c r="H358" t="n">
         <v>1</v>
@@ -15868,7 +15868,7 @@
         <v>0</v>
       </c>
       <c r="G359" t="n">
-        <v>0.204714</v>
+        <v>0.168959</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -15911,7 +15911,7 @@
         <v>0</v>
       </c>
       <c r="G360" t="n">
-        <v>0.312571</v>
+        <v>0.199699</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>0</v>
       </c>
       <c r="G361" t="n">
-        <v>0.383768</v>
+        <v>0.301332</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -15997,7 +15997,7 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>0.7834719999999999</v>
+        <v>0.620165</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
         <v>0</v>
       </c>
       <c r="G363" t="n">
-        <v>0.169576</v>
+        <v>0.321531</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -16083,7 +16083,7 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>0.951193</v>
+        <v>0.836817</v>
       </c>
       <c r="H364" t="n">
         <v>1</v>
@@ -16126,7 +16126,7 @@
         <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>0.199421</v>
+        <v>0.129003</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -16166,10 +16166,10 @@
         <v>0.006855</v>
       </c>
       <c r="F366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G366" t="n">
-        <v>0.377938</v>
+        <v>0.562839</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
         <v>0</v>
       </c>
       <c r="G367" t="n">
-        <v>0.268982</v>
+        <v>0.354566</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -16255,7 +16255,7 @@
         <v>0</v>
       </c>
       <c r="G368" t="n">
-        <v>0.301069</v>
+        <v>0.392217</v>
       </c>
       <c r="H368" t="n">
         <v>1</v>
@@ -16295,10 +16295,10 @@
         <v>0.030001</v>
       </c>
       <c r="F369" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>0.481693</v>
+        <v>0.555898</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -16341,7 +16341,7 @@
         <v>0</v>
       </c>
       <c r="G370" t="n">
-        <v>0.230005</v>
+        <v>0.353173</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -16381,10 +16381,10 @@
         <v>0.170971</v>
       </c>
       <c r="F371" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G371" t="n">
-        <v>0.596774</v>
+        <v>0.486114</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -16427,7 +16427,7 @@
         <v>0</v>
       </c>
       <c r="G372" t="n">
-        <v>0.203614</v>
+        <v>0.169484</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -16470,7 +16470,7 @@
         <v>0</v>
       </c>
       <c r="G373" t="n">
-        <v>0.202637</v>
+        <v>0.280464</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
         <v>0</v>
       </c>
       <c r="G374" t="n">
-        <v>0.321982</v>
+        <v>0.329809</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -16556,7 +16556,7 @@
         <v>0</v>
       </c>
       <c r="G375" t="n">
-        <v>0.350389</v>
+        <v>0.294582</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -16596,10 +16596,10 @@
         <v>0.0005910000000000001</v>
       </c>
       <c r="F376" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G376" t="n">
-        <v>0.673409</v>
+        <v>0.493586</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -16642,7 +16642,7 @@
         <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>0.331485</v>
+        <v>0.229732</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -16685,7 +16685,7 @@
         <v>0</v>
       </c>
       <c r="G378" t="n">
-        <v>0.280305</v>
+        <v>0.282115</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="G379" t="n">
-        <v>0.235453</v>
+        <v>0.192162</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -16768,10 +16768,10 @@
         <v>0.343377</v>
       </c>
       <c r="F380" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G380" t="n">
-        <v>0.5562240000000001</v>
+        <v>0.275208</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -16811,10 +16811,10 @@
         <v>0.884341</v>
       </c>
       <c r="F381" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G381" t="n">
-        <v>0.6329129999999999</v>
+        <v>0.419217</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -16857,7 +16857,7 @@
         <v>0</v>
       </c>
       <c r="G382" t="n">
-        <v>0.412142</v>
+        <v>0.442402</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="G383" t="n">
-        <v>0.244495</v>
+        <v>0.218948</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
         <v>0</v>
       </c>
       <c r="G384" t="n">
-        <v>0.232938</v>
+        <v>0.188971</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>0</v>
       </c>
       <c r="G385" t="n">
-        <v>0.197039</v>
+        <v>0.152166</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -17029,7 +17029,7 @@
         <v>0</v>
       </c>
       <c r="G386" t="n">
-        <v>0.221645</v>
+        <v>0.220357</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -17072,7 +17072,7 @@
         <v>0</v>
       </c>
       <c r="G387" t="n">
-        <v>0.150338</v>
+        <v>0.296064</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -17115,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="G388" t="n">
-        <v>0.280158</v>
+        <v>0.283008</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -17158,7 +17158,7 @@
         <v>0</v>
       </c>
       <c r="G389" t="n">
-        <v>0.194642</v>
+        <v>0.130423</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>0</v>
       </c>
       <c r="G390" t="n">
-        <v>0.277616</v>
+        <v>0.166337</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -17244,7 +17244,7 @@
         <v>0</v>
       </c>
       <c r="G391" t="n">
-        <v>0.205595</v>
+        <v>0.30429</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="G392" t="n">
-        <v>0.315083</v>
+        <v>0.382119</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -17330,7 +17330,7 @@
         <v>0</v>
       </c>
       <c r="G393" t="n">
-        <v>0.31635</v>
+        <v>0.305903</v>
       </c>
       <c r="H393" t="n">
         <v>0</v>
@@ -17373,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="G394" t="n">
-        <v>0.303613</v>
+        <v>0.237699</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -17416,7 +17416,7 @@
         <v>1</v>
       </c>
       <c r="G395" t="n">
-        <v>0.572841</v>
+        <v>0.627594</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -17459,7 +17459,7 @@
         <v>0</v>
       </c>
       <c r="G396" t="n">
-        <v>0.180327</v>
+        <v>0.226626</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -17502,7 +17502,7 @@
         <v>0</v>
       </c>
       <c r="G397" t="n">
-        <v>0.491247</v>
+        <v>0.473193</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -17545,7 +17545,7 @@
         <v>0</v>
       </c>
       <c r="G398" t="n">
-        <v>0.271794</v>
+        <v>0.239645</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -17588,7 +17588,7 @@
         <v>0</v>
       </c>
       <c r="G399" t="n">
-        <v>0.279828</v>
+        <v>0.38253</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -17631,7 +17631,7 @@
         <v>0</v>
       </c>
       <c r="G400" t="n">
-        <v>0.243953</v>
+        <v>0.322595</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -17674,7 +17674,7 @@
         <v>1</v>
       </c>
       <c r="G401" t="n">
-        <v>0.529956</v>
+        <v>0.701254</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -17717,7 +17717,7 @@
         <v>0</v>
       </c>
       <c r="G402" t="n">
-        <v>0.224201</v>
+        <v>0.245987</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -17760,7 +17760,7 @@
         <v>1</v>
       </c>
       <c r="G403" t="n">
-        <v>0.883512</v>
+        <v>0.932595</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -17803,7 +17803,7 @@
         <v>0</v>
       </c>
       <c r="G404" t="n">
-        <v>0.270546</v>
+        <v>0.331906</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -17846,7 +17846,7 @@
         <v>0</v>
       </c>
       <c r="G405" t="n">
-        <v>0.168947</v>
+        <v>0.271758</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -17889,7 +17889,7 @@
         <v>0</v>
       </c>
       <c r="G406" t="n">
-        <v>0.264541</v>
+        <v>0.323728</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -17932,7 +17932,7 @@
         <v>1</v>
       </c>
       <c r="G407" t="n">
-        <v>0.726136</v>
+        <v>0.615605</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -17975,7 +17975,7 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0.981059</v>
+        <v>0.942475</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -18018,7 +18018,7 @@
         <v>0</v>
       </c>
       <c r="G409" t="n">
-        <v>0.2535</v>
+        <v>0.193273</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -18061,7 +18061,7 @@
         <v>0</v>
       </c>
       <c r="G410" t="n">
-        <v>0.204699</v>
+        <v>0.30191</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -18104,7 +18104,7 @@
         <v>0</v>
       </c>
       <c r="G411" t="n">
-        <v>0.471965</v>
+        <v>0.33503</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -18147,7 +18147,7 @@
         <v>0</v>
       </c>
       <c r="G412" t="n">
-        <v>0.294117</v>
+        <v>0.275913</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -18190,7 +18190,7 @@
         <v>0</v>
       </c>
       <c r="G413" t="n">
-        <v>0.189969</v>
+        <v>0.121854</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0.880085</v>
+        <v>0.997417</v>
       </c>
       <c r="H414" t="n">
         <v>1</v>
